--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_235_R24.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_235_R24.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.494</v>
+        <v>7.2511</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8836</v>
+        <v>6.2374</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6104000000000001</v>
+        <v>1.0137</v>
       </c>
       <c r="G2" t="n">
         <v>5.6553</v>
@@ -610,13 +610,13 @@
         <v>1.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1975</v>
+        <v>-0.4404</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1202</v>
+        <v>-0.7664</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.07729999999999999</v>
+        <v>0.326</v>
       </c>
       <c r="V2" t="n">
         <v>2.9641</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.3707</v>
+        <v>5.7561</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5401</v>
+        <v>4.4968</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8306</v>
+        <v>1.2593</v>
       </c>
       <c r="G3" t="n">
         <v>2.6524</v>
@@ -688,13 +688,13 @@
         <v>1.1598</v>
       </c>
       <c r="S3" t="n">
-        <v>0.865</v>
+        <v>0.2504</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0351</v>
+        <v>-0.0784</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9001</v>
+        <v>0.3288</v>
       </c>
       <c r="V3" t="n">
         <v>2.8533</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6444</v>
+        <v>2.8974</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7244</v>
+        <v>1.0783</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9199</v>
+        <v>1.8191</v>
       </c>
       <c r="G4" t="n">
         <v>0.5938</v>
@@ -766,13 +766,13 @@
         <v>1.1598</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1814</v>
+        <v>0.0716</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.1202</v>
+        <v>-0.7664</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9388</v>
+        <v>0.838</v>
       </c>
       <c r="V4" t="n">
         <v>1.0722</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>U. GARUBA</t>
+          <t>C. OKEKE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7379</v>
+        <v>2.0287</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1241</v>
+        <v>0.9528</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6138</v>
+        <v>1.076</v>
       </c>
       <c r="G5" t="n">
-        <v>2.2797</v>
+        <v>1.0675</v>
       </c>
       <c r="H5" t="n">
-        <v>1.761</v>
+        <v>0.5187</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5187</v>
+        <v>0.5488</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4945</v>
+        <v>1.389</v>
       </c>
       <c r="K5" t="n">
-        <v>1.8688</v>
+        <v>0.1008</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6257</v>
+        <v>1.2882</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2148</v>
+        <v>-0.3215</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1078</v>
+        <v>0.4179</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.107</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0.9278</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4556</v>
+        <v>0.0334</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4129</v>
+        <v>-0.4362</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0426</v>
+        <v>0.4696</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3943</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. OKEKE</t>
+          <t>U. GARUBA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5912</v>
+        <v>1.4758</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7169</v>
+        <v>0.9628</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8743</v>
+        <v>0.513</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0675</v>
+        <v>2.2797</v>
       </c>
       <c r="H6" t="n">
+        <v>1.761</v>
+      </c>
+      <c r="I6" t="n">
         <v>0.5187</v>
       </c>
-      <c r="I6" t="n">
-        <v>0.5488</v>
-      </c>
       <c r="J6" t="n">
-        <v>1.389</v>
+        <v>2.4945</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1008</v>
+        <v>1.8688</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2882</v>
+        <v>0.6257</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3215</v>
+        <v>-0.2148</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4179</v>
+        <v>-0.1078</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-0.107</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9278</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R6" t="n">
         <v>0.9278</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4042</v>
+        <v>0.1935</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6721</v>
+        <v>0.2517</v>
       </c>
       <c r="U6" t="n">
-        <v>0.268</v>
+        <v>-0.0582</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>W. TAVARES</t>
+          <t>A. ABALDE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.429</v>
+        <v>0.9113</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.619</v>
+        <v>2.4021</v>
       </c>
       <c r="F7" t="n">
-        <v>1.048</v>
+        <v>-1.4908</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2689</v>
+        <v>1.0031</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6468</v>
+        <v>-1.5064</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.378</v>
+        <v>2.5095</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8227</v>
+        <v>2.0216</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5649999999999999</v>
+        <v>-1.3878</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2576</v>
+        <v>3.4094</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5538</v>
+        <v>-1.0185</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0818</v>
+        <v>-0.1186</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-0.8999</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.3195</v>
+        <v>1.6237</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="S7" t="n">
-        <v>3.1265</v>
+        <v>-0.1072</v>
       </c>
       <c r="T7" t="n">
-        <v>1.6122</v>
+        <v>-0.6917</v>
       </c>
       <c r="U7" t="n">
-        <v>1.5143</v>
+        <v>0.5845</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6468</v>
+        <v>-1.6083</v>
       </c>
       <c r="W7" t="n">
-        <v>0.4254</v>
+        <v>1.0722</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0722</v>
+        <v>-2.6805</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. ABALDE</t>
+          <t>T. MALEDON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1877</v>
+        <v>-0.0702</v>
       </c>
       <c r="E8" t="n">
-        <v>2.0482</v>
+        <v>-0.5341</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.8605</v>
+        <v>0.4639</v>
       </c>
       <c r="G8" t="n">
-        <v>1.0031</v>
+        <v>0.6257</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.5064</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2.5095</v>
+        <v>0.6257</v>
       </c>
       <c r="J8" t="n">
-        <v>2.0216</v>
+        <v>0.6257</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.3878</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3.4094</v>
+        <v>0.6257</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0185</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1186</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8999</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.6237</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6237</v>
+        <v>0.4639</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8307</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0455</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2148</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.6805</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. MALEDON</t>
+          <t>A. LEN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0702</v>
+        <v>-0.4078</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5341</v>
+        <v>-0.7514</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4639</v>
+        <v>0.3436</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6257</v>
+        <v>0.7972</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.6567</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6257</v>
+        <v>0.1406</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6257</v>
+        <v>0.5578</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>0.521</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6257</v>
+        <v>0.0368</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>0.2395</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>0.1357</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>0.1038</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6959</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4639</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0.0452</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>-0.1494</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>0.1041</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. LEN</t>
+          <t>W. TAVARES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.475</v>
+        <v>-1.6922</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7514</v>
+        <v>-2.0344</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2764</v>
+        <v>0.3423</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7972</v>
+        <v>0.2689</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6567</v>
+        <v>0.6468</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1406</v>
+        <v>-0.378</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5578</v>
+        <v>0.8227</v>
       </c>
       <c r="K10" t="n">
-        <v>0.521</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0368</v>
+        <v>0.2576</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2395</v>
+        <v>-0.5538</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1357</v>
+        <v>0.0818</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1038</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.1598</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1125</v>
+        <v>1.0053</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1494</v>
+        <v>0.1968</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0369</v>
+        <v>0.8085</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.6468</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.4254</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.428</v>
+        <v>-2.4548</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.3347</v>
+        <v>-3.4959</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9067</v>
+        <v>1.0411</v>
       </c>
       <c r="G11" t="n">
         <v>-0.894</v>
@@ -1312,13 +1312,13 @@
         <v>0.9278</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1423</v>
+        <v>-0.1691</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1142</v>
+        <v>-0.047</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2565</v>
+        <v>-0.1221</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9574</v>
+        <v>-2.4616</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.1238</v>
+        <v>-2.6952</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1664</v>
+        <v>0.2336</v>
       </c>
       <c r="G12" t="n">
         <v>-1.2003</v>
@@ -1390,13 +1390,13 @@
         <v>0.232</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4349</v>
+        <v>0.0608</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3734</v>
+        <v>0.0551</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0615</v>
+        <v>0.0057</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3943</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.2316</v>
+        <v>-2.5678</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.0644</v>
+        <v>-1.6359</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.1672</v>
+        <v>-0.9319</v>
       </c>
       <c r="G13" t="n">
         <v>0.6244</v>
@@ -1468,13 +1468,13 @@
         <v>0.4639</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9282</v>
+        <v>-0.2645</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3734</v>
+        <v>0.0551</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5548</v>
+        <v>-0.3196</v>
       </c>
       <c r="V13" t="n">
         <v>-1.0722</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>10.2927</v>
+        <v>10.666</v>
       </c>
       <c r="E14" t="n">
-        <v>4.6099</v>
+        <v>4.983300000000003</v>
       </c>
       <c r="F14" t="n">
-        <v>5.6827</v>
+        <v>5.682900000000001</v>
       </c>
       <c r="G14" t="n">
         <v>13.4737</v>
@@ -1546,16 +1546,16 @@
         <v>10.438</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2153999999999999</v>
+        <v>0.5886</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.75</v>
+        <v>-2.3768</v>
       </c>
       <c r="U14" t="n">
-        <v>2.9654</v>
+        <v>2.9653</v>
       </c>
       <c r="V14" t="n">
-        <v>3.5623</v>
+        <v>3.562299999999999</v>
       </c>
       <c r="W14" t="n">
         <v>8.529</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.9408</v>
+        <v>2.5026</v>
       </c>
       <c r="E15" t="n">
-        <v>2.266</v>
+        <v>1.7942</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6748</v>
+        <v>0.7084</v>
       </c>
       <c r="G15" t="n">
         <v>0.4954</v>
@@ -1624,13 +1624,13 @@
         <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6594</v>
+        <v>0.2212</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5623</v>
+        <v>0.0905</v>
       </c>
       <c r="U15" t="n">
-        <v>0.09710000000000001</v>
+        <v>0.1307</v>
       </c>
       <c r="V15" t="n">
         <v>0.3943</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4781</v>
+        <v>1.7888</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7856</v>
+        <v>1.6677</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6924</v>
+        <v>0.1211</v>
       </c>
       <c r="G16" t="n">
         <v>0.2536</v>
@@ -1702,13 +1702,13 @@
         <v>2.0876</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2245</v>
+        <v>-0.4648</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7073</v>
+        <v>-0.8252</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9318</v>
+        <v>0.3605</v>
       </c>
       <c r="V16" t="n">
         <v>1.0722</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0073</v>
+        <v>1.1081</v>
       </c>
       <c r="E17" t="n">
         <v>2.1737</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1664</v>
+        <v>-1.0656</v>
       </c>
       <c r="G17" t="n">
         <v>0.9089</v>
@@ -1780,13 +1780,13 @@
         <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5469000000000001</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="T17" t="n">
         <v>0.2636</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2834</v>
+        <v>0.3842</v>
       </c>
       <c r="V17" t="n">
         <v>-1.6083</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3738</v>
+        <v>0.1557</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4467</v>
+        <v>2.5646</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.0729</v>
+        <v>-2.4089</v>
       </c>
       <c r="G18" t="n">
         <v>-0.6621</v>
@@ -1858,13 +1858,13 @@
         <v>2.7834</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4639</v>
+        <v>0.2458</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.782</v>
+        <v>-0.664</v>
       </c>
       <c r="U18" t="n">
-        <v>1.2459</v>
+        <v>0.9098000000000001</v>
       </c>
       <c r="V18" t="n">
         <v>-0.8197</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>K. HAYES</t>
+          <t>N. NEDOVIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.349</v>
+        <v>-0.3414</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2072</v>
+        <v>-0.0203</v>
       </c>
       <c r="F20" t="n">
+        <v>-0.321</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-0.6734</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-0.4994</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-0.174</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.07389999999999999</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.0371</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.0368</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-0.7473</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-0.5365</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-0.2108</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.4639</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.4639</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.009900000000000001</v>
+      </c>
+      <c r="T20" t="n">
+        <v>-0.09420000000000001</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.1041</v>
+      </c>
+      <c r="V20" t="n">
         <v>-0.1418</v>
       </c>
-      <c r="G20" t="n">
-        <v>-3.2504</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-2.4608</v>
-      </c>
-      <c r="I20" t="n">
-        <v>-0.7896</v>
-      </c>
-      <c r="J20" t="n">
-        <v>-0.6516999999999999</v>
-      </c>
-      <c r="K20" t="n">
-        <v>-1.3878</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0.7361</v>
-      </c>
-      <c r="M20" t="n">
-        <v>-2.5987</v>
-      </c>
-      <c r="N20" t="n">
-        <v>-1.073</v>
-      </c>
-      <c r="O20" t="n">
-        <v>-1.5257</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.3195</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>-0.232</v>
-      </c>
-      <c r="R20" t="n">
-        <v>2.5515</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0.0769</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0.6765</v>
-      </c>
-      <c r="U20" t="n">
-        <v>-0.5996</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0.5051</v>
-      </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.5051</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>N. NEDOVIC</t>
+          <t>K. HAYES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.628</v>
+        <v>-0.6528</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3742</v>
+        <v>-0.679</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2538</v>
+        <v>0.0262</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6734</v>
+        <v>-3.2504</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.4994</v>
+        <v>-2.4608</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.174</v>
+        <v>-0.7896</v>
       </c>
       <c r="J21" t="n">
-        <v>0.07389999999999999</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0371</v>
+        <v>-1.3878</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0368</v>
+        <v>0.7361</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7473</v>
+        <v>-2.5987</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5365</v>
+        <v>-1.073</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2108</v>
+        <v>-1.5257</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4639</v>
+        <v>2.3195</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4639</v>
+        <v>2.5515</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2768</v>
+        <v>-0.2269</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4481</v>
+        <v>0.2047</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1713</v>
+        <v>-0.4316</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1418</v>
+        <v>0.5051</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1418</v>
+        <v>0.5051</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.1221</v>
+        <v>-1.1392</v>
       </c>
       <c r="E22" t="n">
-        <v>1.5976</v>
+        <v>1.4796</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.7197</v>
+        <v>-2.6188</v>
       </c>
       <c r="G22" t="n">
         <v>1.0603</v>
@@ -2170,13 +2170,13 @@
         <v>0.9278</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2482</v>
+        <v>0.2311</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4086</v>
+        <v>-0.5265</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6568000000000001</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="V22" t="n">
         <v>-3.3584</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.2098</v>
+        <v>-3.5871</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.9954</v>
+        <v>-4.6415</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7855</v>
+        <v>1.0544</v>
       </c>
       <c r="G23" t="n">
         <v>-1.6991</v>
@@ -2248,13 +2248,13 @@
         <v>1.8556</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5676</v>
+        <v>0.0551</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3339</v>
+        <v>0.02</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2337</v>
+        <v>0.0351</v>
       </c>
       <c r="V23" t="n">
         <v>1.0722</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. DIALLO</t>
+          <t>E. OKOBO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.3341</v>
+        <v>-5.0218</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.4569</v>
+        <v>-4.2621</v>
       </c>
       <c r="F24" t="n">
-        <v>1.1228</v>
+        <v>-0.7596000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.235</v>
+        <v>-5.6719</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.0793</v>
+        <v>-4.2967</v>
       </c>
       <c r="I24" t="n">
-        <v>-4.1557</v>
+        <v>-1.3752</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.0488</v>
+        <v>-3.5235</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.9474</v>
+        <v>-3.2021</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.1014</v>
+        <v>-0.3213</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.1861</v>
+        <v>-2.1484</v>
       </c>
       <c r="N24" t="n">
-        <v>0.8681</v>
+        <v>-1.0945</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.0543</v>
+        <v>-1.0539</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.4639</v>
+        <v>1.8556</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.5515</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.0876</v>
+        <v>1.8556</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6352</v>
+        <v>-0.5276</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8566</v>
+        <v>-0.7387</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2214</v>
+        <v>0.2111</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>E. OKOBO</t>
+          <t>A. DIALLO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.375</v>
+        <v>-5.031</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.3801</v>
+        <v>-6.221</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.9949</v>
+        <v>1.19</v>
       </c>
       <c r="G25" t="n">
-        <v>-5.6719</v>
+        <v>-4.235</v>
       </c>
       <c r="H25" t="n">
-        <v>-4.2967</v>
+        <v>-0.0793</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.3752</v>
+        <v>-4.1557</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.5235</v>
+        <v>-3.0488</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.2021</v>
+        <v>-0.9474</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.3213</v>
+        <v>-2.1014</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.1484</v>
+        <v>-1.1861</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.0945</v>
+        <v>0.8681</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.0539</v>
+        <v>-2.0543</v>
       </c>
       <c r="P25" t="n">
-        <v>1.8556</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>-2.5515</v>
       </c>
       <c r="R25" t="n">
-        <v>1.8556</v>
+        <v>2.0876</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.8808</v>
+        <v>-0.3321</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8566</v>
+        <v>-0.6207</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0242</v>
+        <v>0.2886</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-10.2927</v>
+        <v>-10.2928</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.2189</v>
+        <v>-6.218799999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-4.074000000000001</v>
+        <v>-4.0738</v>
       </c>
       <c r="G26" t="n">
         <v>-13.4737</v>
@@ -2455,7 +2455,7 @@
         <v>-8.917400000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>2.753700000000001</v>
+        <v>2.7537</v>
       </c>
       <c r="K26" t="n">
         <v>0.3457000000000003</v>
@@ -2482,13 +2482,13 @@
         <v>17.3964</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.2152999999999996</v>
+        <v>-0.2152999999999998</v>
       </c>
       <c r="T26" t="n">
-        <v>-2.9654</v>
+        <v>-2.9652</v>
       </c>
       <c r="U26" t="n">
-        <v>2.7502</v>
+        <v>2.7501</v>
       </c>
       <c r="V26" t="n">
         <v>-3.5623</v>
